--- a/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97B12AF-5CB4-4942-A7A0-006A5C865B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7389FEBD-88E6-4C5C-BAC4-60873697DED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
+    <workbookView xWindow="6075" yWindow="9600" windowWidth="28800" windowHeight="16905" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -212,12 +212,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4887,16 +4887,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B321D7-C433-4B50-AA6E-BF1C75F28F7F}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.83984375" customWidth="1"/>
-    <col min="2" max="2" width="13.15625" customWidth="1"/>
-    <col min="3" max="3" width="15.578125" customWidth="1"/>
-    <col min="4" max="5" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="8.89453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4922,7 +4922,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4933,14 +4933,14 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -4948,7 +4948,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -4975,7 +4975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1881</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>19.801490062127176</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f>A6+1</f>
         <v>1882</v>
@@ -5046,7 +5046,7 @@
         <v>19.415967691829763</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" ref="A8:A38" si="4">A7+1</f>
         <v>1883</v>
@@ -5084,7 +5084,7 @@
         <v>19.04498902532508</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="4"/>
         <v>1884</v>
@@ -5122,7 +5122,7 @@
         <v>18.687746444656238</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f t="shared" si="4"/>
         <v>1885</v>
@@ -5160,7 +5160,7 @@
         <v>18.343491041497558</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <f t="shared" si="4"/>
         <v>1886</v>
@@ -5198,7 +5198,7 @@
         <v>18.01152737752161</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <f t="shared" si="4"/>
         <v>1887</v>
@@ -5236,7 +5236,7 @@
         <v>17.691208796069017</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="4"/>
         <v>1888</v>
@@ -5274,7 +5274,7 @@
         <v>17.38193321861257</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="4"/>
         <v>1889</v>
@@ -5312,7 +5312,7 @@
         <v>17.083139368521753</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="4"/>
         <v>1890</v>
@@ -5350,7 +5350,7 @@
         <v>16.794303372296117</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="4"/>
         <v>1891</v>
@@ -5388,7 +5388,7 @@
         <v>16.514935694969136</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="4"/>
         <v>1892</v>
@@ -5426,7 +5426,7 @@
         <v>16.244578371968352</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="4"/>
         <v>1893</v>
@@ -5464,7 +5464,7 @@
         <v>15.982802504505155</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="4"/>
         <v>1894</v>
@@ -5502,7 +5502,7 @@
         <v>15.729205989681645</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="4"/>
         <v>1895</v>
@@ -5540,7 +5540,7 @@
         <v>15.483411460046998</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="4"/>
         <v>1896</v>
@@ -5578,7 +5578,7 @@
         <v>15.245064410397131</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="4"/>
         <v>1897</v>
@@ -5616,7 +5616,7 @@
         <v>15.013831492262245</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <f t="shared" si="4"/>
         <v>1898</v>
@@ -5654,7 +5654,7 @@
         <v>14.789398958826315</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="4"/>
         <v>1899</v>
@@ -5692,7 +5692,7 @@
         <v>14.571471245022931</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="4"/>
         <v>1900</v>
@@ -5730,7 +5730,7 @@
         <v>14.359769669294504</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="4"/>
         <v>1901</v>
@@ -5768,7 +5768,7 @@
         <v>14.154031245023972</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="4"/>
         <v>1902</v>
@@ -5806,7 +5806,7 @@
         <v>13.95400759098013</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f t="shared" si="4"/>
         <v>1903</v>
@@ -5844,7 +5844,7 @@
         <v>13.759463931285243</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="4"/>
         <v>1904</v>
@@ -5882,7 +5882,7 @@
         <v>13.570178176439455</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="4"/>
         <v>1905</v>
@@ -5920,7 +5920,7 @@
         <v>13.385940077839233</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="4"/>
         <v>1906</v>
@@ -5958,7 +5958,7 @@
         <v>13.206550449022718</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="4"/>
         <v>1907</v>
@@ -5996,7 +5996,7 @@
         <v>13.031820447577875</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="4"/>
         <v>1908</v>
@@ -6034,7 +6034,7 @@
         <v>12.861570912271226</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="4"/>
         <v>1909</v>
@@ -6072,7 +6072,7 @@
         <v>12.695631750505445</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="4"/>
         <v>1910</v>
@@ -6110,7 +6110,7 @@
         <v>12.533841371703598</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="4"/>
         <v>1911</v>
@@ -6148,7 +6148,7 @@
         <v>12.376046162652191</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="4"/>
         <v>1912</v>
@@ -6186,7 +6186,7 @@
         <v>12.222100001222209</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="4"/>
         <v>1913</v>
@@ -6224,7 +6224,7 @@
         <v>12.07186380523255</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f>A38+1</f>
         <v>1914</v>
@@ -6241,7 +6241,7 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -6252,95 +6252,95 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A41" s="11" t="s">
+    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="12" cm="1">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="11" cm="1">
         <f t="array" ref="D41">SUM(D6+D6:D20)</f>
         <v>1510500</v>
       </c>
-      <c r="E41" s="12" cm="1">
+      <c r="E41" s="11" cm="1">
         <f t="array" ref="E41">SUM(E6+E6:E20)</f>
         <v>910500</v>
       </c>
-      <c r="F41" s="12" cm="1">
+      <c r="F41" s="11" cm="1">
         <f t="array" ref="F41">SUM(F6+F6:F20)</f>
         <v>2550</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="12">
         <f>AVERAGE(G6:G20)</f>
         <v>44.284960471317206</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H41" s="12">
         <f>AVERAGE(H6:H20)</f>
         <v>26.804245110008651</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="12">
         <f>AVERAGE(I6:I20)</f>
         <v>17.480715361308548</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A42" s="11" t="s">
+    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="12">
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11">
         <f>SUM(D21:D39)</f>
         <v>942300</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="11">
         <f>SUM(E21:E39)</f>
         <v>582300</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="11">
         <f>SUM(F21:F39)</f>
         <v>5130</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="12">
         <f>AVERAGE(G21:G38)</f>
         <v>35.4279467724824</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="12">
         <f>AVERAGE(H21:H38)</f>
         <v>21.883358900395795</v>
       </c>
-      <c r="I42" s="13">
+      <c r="I42" s="12">
         <f>AVERAGE(I21:I38)</f>
         <v>13.544587872086607</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A43" s="11" t="s">
+    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="12">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="11">
         <f>D41+D42</f>
         <v>2452800</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="11">
         <f>E41+E42</f>
         <v>1492800</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="11">
         <f>F41+F42</f>
         <v>7680</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="12">
         <f>AVERAGE(G6:G38)</f>
         <v>39.453862090134571</v>
       </c>
-      <c r="H43" s="13">
+      <c r="H43" s="12">
         <f>AVERAGE(H6:H38)</f>
         <v>24.12012535931073</v>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="12">
         <f>AVERAGE(I6:I38)</f>
         <v>15.333736730823857</v>
       </c>
